--- a/report_templates/CANTEEN-REPORT-2025-2026-2 (1).xlsx
+++ b/report_templates/CANTEEN-REPORT-2025-2026-2 (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d83244719a67419/Desktop/New folder (11)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronal\AppData\Local\Temp\fz3temp-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D74D8BFD-E914-4CA7-BBD0-84A2922F45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FBBDD4C-FA99-45CB-B7D8-97EDF905FA4D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06168DF-6C95-4AFF-B108-5489D9069348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="65">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>For the Month of May 2026</t>
+  </si>
+  <si>
+    <t>JOHN DIERIC V. ISLETA</t>
+  </si>
+  <si>
+    <t>Adminitrative Officer II</t>
   </si>
 </sst>
 </file>
@@ -831,53 +837,18 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -898,11 +869,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1604,7 +1610,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -1614,7 +1620,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -1624,7 +1630,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -1634,7 +1640,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -1643,7 +1649,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -1655,7 +1661,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -1667,7 +1673,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -1679,7 +1685,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -1691,7 +1697,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -1703,7 +1709,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -1715,7 +1721,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -1724,7 +1730,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -1736,7 +1742,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="48"/>
@@ -1795,10 +1801,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="54">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="68">
+        <v>0</v>
+      </c>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -1808,10 +1814,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -1821,11 +1827,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -1855,10 +1861,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -1868,10 +1874,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -1881,10 +1887,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -1894,10 +1900,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -1907,10 +1913,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -1920,10 +1926,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -1933,10 +1939,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -1946,7 +1952,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -1969,8 +1975,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -1991,7 +1997,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -2004,7 +2010,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -2017,7 +2023,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -2032,7 +2038,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -2042,11 +2048,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -2266,7 +2272,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -2274,23 +2280,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -2302,7 +2308,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -2315,7 +2321,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -2323,7 +2329,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -2350,18 +2356,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -4822,12 +4828,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -4840,31 +4865,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -4885,7 +4891,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -4895,7 +4901,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4905,7 +4911,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -4915,7 +4921,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -4924,7 +4930,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -4936,7 +4942,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -4948,7 +4954,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -4960,7 +4966,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -4972,7 +4978,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -4984,7 +4990,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -4996,7 +5002,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -5005,7 +5011,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -5017,7 +5023,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="48"/>
@@ -5077,10 +5083,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -5090,10 +5096,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -5103,11 +5109,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -5137,10 +5143,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -5150,10 +5156,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -5163,10 +5169,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -5176,10 +5182,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -5189,10 +5195,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -5202,10 +5208,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -5215,10 +5221,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -5228,7 +5234,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -5251,8 +5257,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -5273,7 +5279,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -5286,7 +5292,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -5299,7 +5305,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -5314,7 +5320,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -5324,11 +5330,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -5554,7 +5560,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -5562,23 +5568,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -5590,7 +5596,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -5603,7 +5609,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -5611,7 +5617,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -5638,18 +5644,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -8110,12 +8116,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -8128,31 +8153,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8174,7 +8180,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -8184,7 +8190,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -8194,7 +8200,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -8204,7 +8210,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -8213,7 +8219,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -8225,7 +8231,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -8237,7 +8243,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -8249,7 +8255,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -8261,7 +8267,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -8273,7 +8279,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -8285,7 +8291,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -8294,7 +8300,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -8306,7 +8312,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="48"/>
@@ -8366,10 +8372,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -8379,10 +8385,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -8392,11 +8398,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -8426,10 +8432,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -8439,10 +8445,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -8452,10 +8458,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -8465,10 +8471,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -8478,10 +8484,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -8491,10 +8497,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -8504,10 +8510,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -8517,7 +8523,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -8540,8 +8546,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -8562,7 +8568,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -8575,7 +8581,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -8588,7 +8594,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -8603,7 +8609,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -8613,11 +8619,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -8843,7 +8849,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -8851,23 +8857,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -8879,7 +8885,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -8892,7 +8898,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -8900,7 +8906,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -8927,18 +8933,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -11399,12 +11405,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -11417,31 +11442,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11462,7 +11468,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -11472,7 +11478,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -11482,7 +11488,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -11492,7 +11498,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -11501,7 +11507,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -11513,7 +11519,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -11525,7 +11531,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -11537,7 +11543,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -11549,7 +11555,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -11561,7 +11567,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -11573,7 +11579,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -11582,7 +11588,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -11594,7 +11600,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="48"/>
@@ -11654,10 +11660,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -11667,10 +11673,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -11680,11 +11686,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -11714,10 +11720,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -11727,10 +11733,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -11740,10 +11746,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -11753,10 +11759,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -11766,10 +11772,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -11779,10 +11785,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -11792,10 +11798,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -11805,7 +11811,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -11828,8 +11834,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -11850,7 +11856,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -11863,7 +11869,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -11876,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -11891,7 +11897,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -11901,11 +11907,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -12131,7 +12137,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -12139,23 +12145,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -12167,7 +12173,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -12180,7 +12186,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -12188,7 +12194,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -12215,18 +12221,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -14687,12 +14693,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -14705,31 +14730,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="75" orientation="portrait"/>
@@ -14750,7 +14756,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -14760,7 +14766,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -14770,7 +14776,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -14780,7 +14786,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -14789,7 +14795,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -14801,7 +14807,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -14813,7 +14819,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -14825,7 +14831,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -14837,7 +14843,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -14849,7 +14855,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -14861,7 +14867,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -14870,7 +14876,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -14882,7 +14888,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="48"/>
@@ -14941,10 +14947,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="54">
-        <v>0</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="68">
+        <v>0</v>
+      </c>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -14954,10 +14960,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -14967,11 +14973,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -15001,10 +15007,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -15014,10 +15020,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -15027,10 +15033,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -15040,10 +15046,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -15053,10 +15059,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -15066,10 +15072,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -15079,10 +15085,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -15092,7 +15098,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -15115,8 +15121,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -15137,7 +15143,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -15150,7 +15156,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -15163,7 +15169,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -15178,7 +15184,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -15188,11 +15194,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -15412,7 +15418,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -15420,23 +15426,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -15448,7 +15454,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -15461,7 +15467,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -15469,7 +15475,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -15496,18 +15502,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -17968,12 +17974,30 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
@@ -17987,30 +18011,12 @@
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="E51:F51"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.65" right="0.7" top="0.31" bottom="0.31" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait"/>
@@ -18031,7 +18037,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -18041,7 +18047,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -18051,7 +18057,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -18061,7 +18067,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -18070,7 +18076,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -18082,7 +18088,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -18094,7 +18100,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -18106,7 +18112,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -18118,7 +18124,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -18130,7 +18136,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -18142,7 +18148,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -18151,7 +18157,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -18163,7 +18169,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="48"/>
@@ -18224,10 +18230,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -18237,10 +18243,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -18250,11 +18256,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -18284,10 +18290,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -18297,10 +18303,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -18310,10 +18316,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -18323,10 +18329,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -18336,10 +18342,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -18349,10 +18355,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -18362,10 +18368,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -18375,7 +18381,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -18398,8 +18404,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -18420,7 +18426,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -18433,7 +18439,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -18446,7 +18452,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -18461,7 +18467,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -18471,11 +18477,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -18701,7 +18707,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -18709,23 +18715,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -18737,7 +18743,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -18750,7 +18756,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -18758,7 +18764,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -18785,18 +18791,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -21257,12 +21263,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -21275,31 +21300,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -21322,7 +21328,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -21332,7 +21338,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -21342,7 +21348,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -21352,7 +21358,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -21361,7 +21367,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -21373,7 +21379,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -21385,7 +21391,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -21397,7 +21403,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -21409,7 +21415,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -21421,7 +21427,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -21433,7 +21439,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -21442,7 +21448,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -21454,7 +21460,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="48"/>
@@ -21514,10 +21520,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -21527,10 +21533,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -21540,11 +21546,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -21574,10 +21580,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -21587,10 +21593,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -21600,10 +21606,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -21613,10 +21619,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -21626,10 +21632,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -21639,10 +21645,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -21652,10 +21658,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -21665,7 +21671,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -21688,8 +21694,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -21710,7 +21716,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -21723,7 +21729,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -21736,7 +21742,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -21751,7 +21757,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -21761,11 +21767,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -21991,7 +21997,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -21999,23 +22005,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
-        <v>44</v>
+      <c r="A50" s="47" t="s">
+        <v>63</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
-        <v>46</v>
+      <c r="A51" s="49" t="s">
+        <v>64</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -22027,7 +22033,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -22040,7 +22046,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -22048,7 +22054,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -22075,18 +22081,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65" t="s">
+      <c r="D62" s="49" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="48"/>
@@ -24549,12 +24555,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -24567,31 +24592,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -24613,7 +24619,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -24623,7 +24629,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -24633,7 +24639,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -24643,7 +24649,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -24652,7 +24658,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -24664,7 +24670,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -24676,7 +24682,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -24688,7 +24694,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -24700,7 +24706,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -24712,7 +24718,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -24724,7 +24730,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -24733,7 +24739,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -24745,7 +24751,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.4">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="48"/>
@@ -24805,10 +24811,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.4">
       <c r="A17" s="8" t="s">
@@ -24818,10 +24824,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.4">
       <c r="A18" s="8" t="s">
@@ -24831,11 +24837,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -24865,10 +24871,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
@@ -24878,10 +24884,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
@@ -24891,10 +24897,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
@@ -24904,10 +24910,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -24917,10 +24923,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
@@ -24930,10 +24936,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
@@ -24943,10 +24949,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -24956,7 +24962,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -24979,8 +24985,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -25001,7 +25007,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -25014,7 +25020,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -25027,7 +25033,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -25042,7 +25048,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -25052,11 +25058,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -25282,7 +25288,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -25290,23 +25296,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -25318,7 +25324,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -25331,7 +25337,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -25339,7 +25345,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -25366,18 +25372,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -27838,12 +27844,31 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -27856,31 +27881,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -27903,7 +27909,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -27913,7 +27919,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -27923,7 +27929,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -27933,7 +27939,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -27942,7 +27948,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -27954,7 +27960,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -27966,7 +27972,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -27978,7 +27984,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -27990,7 +27996,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -28002,7 +28008,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -28014,7 +28020,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -28023,7 +28029,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -28035,7 +28041,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="48"/>
@@ -28095,10 +28101,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -28108,10 +28114,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -28121,11 +28127,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -28155,10 +28161,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -28168,10 +28174,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -28181,10 +28187,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -28194,10 +28200,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -28207,10 +28213,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -28220,10 +28226,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -28233,10 +28239,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -28246,7 +28252,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -28269,8 +28275,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -28291,7 +28297,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -28304,7 +28310,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -28317,7 +28323,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -28332,7 +28338,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -28342,11 +28348,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -28572,7 +28578,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -28580,23 +28586,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -28608,7 +28614,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -28621,7 +28627,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -28629,7 +28635,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -28656,18 +28662,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -31128,12 +31134,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -31146,31 +31171,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -31192,7 +31198,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -31202,7 +31208,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -31212,7 +31218,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -31222,7 +31228,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -31231,7 +31237,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -31243,7 +31249,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -31255,7 +31261,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -31267,7 +31273,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -31279,7 +31285,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -31291,7 +31297,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -31303,7 +31309,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -31312,7 +31318,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -31324,7 +31330,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="48"/>
@@ -31384,10 +31390,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -31397,10 +31403,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -31410,11 +31416,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -31444,10 +31450,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -31457,10 +31463,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -31470,10 +31476,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -31483,10 +31489,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -31496,10 +31502,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -31509,10 +31515,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -31522,10 +31528,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -31535,7 +31541,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -31558,8 +31564,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -31580,7 +31586,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -31593,7 +31599,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -31606,7 +31612,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -31621,7 +31627,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -31631,11 +31637,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -31861,7 +31867,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -31869,23 +31875,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -31897,7 +31903,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -31910,7 +31916,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -31918,7 +31924,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -31945,18 +31951,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -34417,12 +34423,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -34435,31 +34460,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait"/>
@@ -34480,7 +34486,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="47"/>
+      <c r="A1" s="72"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -34490,7 +34496,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="47"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -34500,7 +34506,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -34510,7 +34516,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -34519,7 +34525,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -34531,7 +34537,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -34543,7 +34549,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -34555,7 +34561,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -34567,7 +34573,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -34579,7 +34585,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -34591,7 +34597,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -34600,7 +34606,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -34612,7 +34618,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="48"/>
@@ -34672,10 +34678,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -34685,10 +34691,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -34698,11 +34704,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -34732,10 +34738,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -34745,10 +34751,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -34758,10 +34764,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -34771,10 +34777,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -34784,10 +34790,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -34797,10 +34803,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -34810,10 +34816,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -34823,7 +34829,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -34846,8 +34852,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -34868,7 +34874,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -34881,7 +34887,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -34894,7 +34900,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -34909,7 +34915,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -34919,11 +34925,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -35149,7 +35155,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -35157,23 +35163,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -35185,7 +35191,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -35198,7 +35204,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -35206,7 +35212,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -35233,18 +35239,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -37705,12 +37711,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -37723,31 +37748,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -37768,7 +37774,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="51"/>
+      <c r="A1" s="70"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -37778,7 +37784,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="52"/>
+      <c r="A2" s="71"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -37788,7 +37794,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="47"/>
+      <c r="A3" s="72"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -37798,7 +37804,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -37807,7 +37813,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="48"/>
@@ -37819,7 +37825,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="48"/>
@@ -37831,7 +37837,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="48"/>
@@ -37843,7 +37849,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="48"/>
@@ -37855,7 +37861,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="71" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="48"/>
@@ -37867,7 +37873,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="71" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="48"/>
@@ -37879,7 +37885,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -37888,7 +37894,7 @@
       <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="67" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="48"/>
@@ -37900,7 +37906,7 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="67" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="48"/>
@@ -37960,10 +37966,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="57"/>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="60"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -37973,10 +37979,10 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="56">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57"/>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -37986,11 +37992,11 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="58">
+      <c r="F18" s="63">
         <f>F16-F17</f>
         <v>0</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="60"/>
     </row>
     <row r="19" spans="1:7" ht="7.5" customHeight="1">
       <c r="A19" s="8"/>
@@ -38020,10 +38026,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="55"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51"/>
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="8"/>
@@ -38033,10 +38039,10 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="60">
-        <v>0</v>
-      </c>
-      <c r="G22" s="57"/>
+      <c r="F22" s="59">
+        <v>0</v>
+      </c>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="8"/>
@@ -38046,10 +38052,10 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="61">
-        <v>0</v>
-      </c>
-      <c r="G23" s="57"/>
+      <c r="F23" s="65">
+        <v>0</v>
+      </c>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
       <c r="A24" s="8"/>
@@ -38059,10 +38065,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="57"/>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -38072,10 +38078,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="60">
-        <v>0</v>
-      </c>
-      <c r="G25" s="57"/>
+      <c r="F25" s="59">
+        <v>0</v>
+      </c>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="8"/>
@@ -38085,10 +38091,10 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="60">
-        <v>0</v>
-      </c>
-      <c r="G26" s="57"/>
+      <c r="F26" s="59">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60"/>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1">
       <c r="A27" s="8"/>
@@ -38098,10 +38104,10 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="60">
-        <v>0</v>
-      </c>
-      <c r="G27" s="57"/>
+      <c r="F27" s="59">
+        <v>0</v>
+      </c>
+      <c r="G27" s="60"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="8" t="s">
@@ -38111,7 +38117,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="62">
+      <c r="F28" s="61">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
@@ -38134,8 +38140,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="55"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="51"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
@@ -38156,7 +38162,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="64"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="48"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8">
@@ -38169,7 +38175,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="64"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="48"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
@@ -38182,7 +38188,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="64"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="48"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8">
@@ -38197,7 +38203,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="10"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="68">
+      <c r="F35" s="55">
         <f>I37</f>
         <v>0</v>
       </c>
@@ -38207,11 +38213,11 @@
       <c r="A36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="69"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="48"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="70">
+      <c r="F36" s="57">
         <f>F18-F28</f>
         <v>0</v>
       </c>
@@ -38437,7 +38443,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="58"/>
       <c r="C49" s="48"/>
       <c r="D49" s="48"/>
       <c r="E49" s="41"/>
@@ -38445,23 +38451,23 @@
       <c r="G49" s="41"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B50" s="48"/>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="47" t="s">
         <v>45</v>
       </c>
       <c r="F50" s="48"/>
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="49" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="8"/>
-      <c r="E51" s="67" t="s">
+      <c r="E51" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="48"/>
@@ -38473,7 +38479,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A54" s="66"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="48"/>
       <c r="C54" s="8" t="s">
         <v>48</v>
@@ -38486,7 +38492,7 @@
       <c r="C55" s="43"/>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A56" s="72"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="48"/>
       <c r="C56" s="44" t="s">
         <v>49</v>
@@ -38494,7 +38500,7 @@
       <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A57" s="65"/>
+      <c r="A57" s="49"/>
       <c r="B57" s="48"/>
       <c r="C57" s="2" t="s">
         <v>50</v>
@@ -38521,18 +38527,18 @@
       <c r="G60" s="8"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="50"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="8"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="55"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A62" s="65"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="48"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="65"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="48"/>
       <c r="F62" s="48"/>
       <c r="G62" s="48"/>
@@ -40993,12 +40999,31 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
@@ -41011,31 +41036,12 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="E50:F50"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
